--- a/content/KPIM/02_campaigns/CMP-2026-Q1/CMP-2026-Q1.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q1/CMP-2026-Q1.xlsx
@@ -10518,15 +10518,11 @@
           <t>2026-07-21 22:58:32</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>skipped</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L2"/>
@@ -10554,7 +10550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AA165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10723,6 +10719,9026 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>535</v>
+      </c>
+      <c r="G2" t="n">
+        <v>365</v>
+      </c>
+      <c r="H2" t="n">
+        <v>365</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X2" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>404</v>
+      </c>
+      <c r="G3" t="n">
+        <v>276</v>
+      </c>
+      <c r="H3" t="n">
+        <v>276</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>281</v>
+      </c>
+      <c r="G4" t="n">
+        <v>192</v>
+      </c>
+      <c r="H4" t="n">
+        <v>192</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>195</v>
+      </c>
+      <c r="G5" t="n">
+        <v>133</v>
+      </c>
+      <c r="H5" t="n">
+        <v>133</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>157</v>
+      </c>
+      <c r="G6" t="n">
+        <v>107</v>
+      </c>
+      <c r="H6" t="n">
+        <v>107</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105</v>
+      </c>
+      <c r="G7" t="n">
+        <v>72</v>
+      </c>
+      <c r="H7" t="n">
+        <v>72</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>81</v>
+      </c>
+      <c r="G8" t="n">
+        <v>56</v>
+      </c>
+      <c r="H8" t="n">
+        <v>56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>59</v>
+      </c>
+      <c r="G9" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>38</v>
+      </c>
+      <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="n">
+        <v>26</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H11" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>958</v>
+      </c>
+      <c r="G14" t="n">
+        <v>678</v>
+      </c>
+      <c r="H14" t="n">
+        <v>678</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>719</v>
+      </c>
+      <c r="G15" t="n">
+        <v>509</v>
+      </c>
+      <c r="H15" t="n">
+        <v>509</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>532</v>
+      </c>
+      <c r="G16" t="n">
+        <v>376</v>
+      </c>
+      <c r="H16" t="n">
+        <v>376</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>345</v>
+      </c>
+      <c r="G17" t="n">
+        <v>244</v>
+      </c>
+      <c r="H17" t="n">
+        <v>244</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>303</v>
+      </c>
+      <c r="G18" t="n">
+        <v>214</v>
+      </c>
+      <c r="H18" t="n">
+        <v>214</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>194</v>
+      </c>
+      <c r="G19" t="n">
+        <v>137</v>
+      </c>
+      <c r="H19" t="n">
+        <v>137</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="G20" t="n">
+        <v>105</v>
+      </c>
+      <c r="H20" t="n">
+        <v>105</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>114</v>
+      </c>
+      <c r="G21" t="n">
+        <v>80</v>
+      </c>
+      <c r="H21" t="n">
+        <v>80</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" t="n">
+        <v>57</v>
+      </c>
+      <c r="H22" t="n">
+        <v>57</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>49</v>
+      </c>
+      <c r="G23" t="n">
+        <v>34</v>
+      </c>
+      <c r="H23" t="n">
+        <v>34</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2088</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1298</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1298</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>828</v>
+      </c>
+      <c r="P24" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>48</v>
+      </c>
+      <c r="X24" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1355</v>
+      </c>
+      <c r="G25" t="n">
+        <v>842</v>
+      </c>
+      <c r="H25" t="n">
+        <v>842</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>537</v>
+      </c>
+      <c r="P25" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>30</v>
+      </c>
+      <c r="X25" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G26" t="n">
+        <v>624</v>
+      </c>
+      <c r="H26" t="n">
+        <v>624</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>398</v>
+      </c>
+      <c r="P26" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>23</v>
+      </c>
+      <c r="X26" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>795</v>
+      </c>
+      <c r="G27" t="n">
+        <v>494</v>
+      </c>
+      <c r="H27" t="n">
+        <v>494</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>315</v>
+      </c>
+      <c r="P27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>17</v>
+      </c>
+      <c r="X27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>435</v>
+      </c>
+      <c r="G28" t="n">
+        <v>270</v>
+      </c>
+      <c r="H28" t="n">
+        <v>270</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>173</v>
+      </c>
+      <c r="P28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="X28" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>371</v>
+      </c>
+      <c r="G29" t="n">
+        <v>231</v>
+      </c>
+      <c r="H29" t="n">
+        <v>231</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>147</v>
+      </c>
+      <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229</v>
+      </c>
+      <c r="G30" t="n">
+        <v>142</v>
+      </c>
+      <c r="H30" t="n">
+        <v>142</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>91</v>
+      </c>
+      <c r="P30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>174</v>
+      </c>
+      <c r="G31" t="n">
+        <v>109</v>
+      </c>
+      <c r="H31" t="n">
+        <v>109</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>69</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>48396</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1781</v>
+      </c>
+      <c r="L32" t="n">
+        <v>163.2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>39</v>
+      </c>
+      <c r="N32" t="n">
+        <v>4844.3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>10</v>
+      </c>
+      <c r="R32" t="n">
+        <v>15</v>
+      </c>
+      <c r="S32" t="n">
+        <v>66</v>
+      </c>
+      <c r="U32" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1134</v>
+      </c>
+      <c r="G33" t="n">
+        <v>748</v>
+      </c>
+      <c r="H33" t="n">
+        <v>748</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="X33" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>683</v>
+      </c>
+      <c r="G34" t="n">
+        <v>451</v>
+      </c>
+      <c r="H34" t="n">
+        <v>451</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="X34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>559</v>
+      </c>
+      <c r="G35" t="n">
+        <v>369</v>
+      </c>
+      <c r="H35" t="n">
+        <v>369</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>357</v>
+      </c>
+      <c r="G36" t="n">
+        <v>236</v>
+      </c>
+      <c r="H36" t="n">
+        <v>236</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>265</v>
+      </c>
+      <c r="G37" t="n">
+        <v>175</v>
+      </c>
+      <c r="H37" t="n">
+        <v>175</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>181</v>
+      </c>
+      <c r="G38" t="n">
+        <v>120</v>
+      </c>
+      <c r="H38" t="n">
+        <v>120</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>140</v>
+      </c>
+      <c r="G39" t="n">
+        <v>92</v>
+      </c>
+      <c r="H39" t="n">
+        <v>92</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101</v>
+      </c>
+      <c r="G40" t="n">
+        <v>67</v>
+      </c>
+      <c r="H40" t="n">
+        <v>67</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>60</v>
+      </c>
+      <c r="G41" t="n">
+        <v>39</v>
+      </c>
+      <c r="H41" t="n">
+        <v>39</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>46</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>33</v>
+      </c>
+      <c r="G43" t="n">
+        <v>21</v>
+      </c>
+      <c r="H43" t="n">
+        <v>21</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>24</v>
+      </c>
+      <c r="G44" t="n">
+        <v>16</v>
+      </c>
+      <c r="H44" t="n">
+        <v>16</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13</v>
+      </c>
+      <c r="H45" t="n">
+        <v>13</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3808</v>
+      </c>
+      <c r="G47" t="n">
+        <v>2350</v>
+      </c>
+      <c r="H47" t="n">
+        <v>896</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1455</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2232</v>
+      </c>
+      <c r="P47" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>9</v>
+      </c>
+      <c r="S47" t="n">
+        <v>44</v>
+      </c>
+      <c r="X47" t="n">
+        <v>83</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2890</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1784</v>
+      </c>
+      <c r="H48" t="n">
+        <v>680</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1104</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1694</v>
+      </c>
+      <c r="P48" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7</v>
+      </c>
+      <c r="S48" t="n">
+        <v>33</v>
+      </c>
+      <c r="X48" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2488</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1536</v>
+      </c>
+      <c r="H49" t="n">
+        <v>585</v>
+      </c>
+      <c r="I49" t="n">
+        <v>950</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1458</v>
+      </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S49" t="n">
+        <v>29</v>
+      </c>
+      <c r="X49" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1522</v>
+      </c>
+      <c r="G50" t="n">
+        <v>939</v>
+      </c>
+      <c r="H50" t="n">
+        <v>358</v>
+      </c>
+      <c r="I50" t="n">
+        <v>581</v>
+      </c>
+      <c r="J50" t="n">
+        <v>892</v>
+      </c>
+      <c r="P50" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" t="n">
+        <v>4</v>
+      </c>
+      <c r="S50" t="n">
+        <v>18</v>
+      </c>
+      <c r="X50" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>972</v>
+      </c>
+      <c r="G51" t="n">
+        <v>600</v>
+      </c>
+      <c r="H51" t="n">
+        <v>229</v>
+      </c>
+      <c r="I51" t="n">
+        <v>372</v>
+      </c>
+      <c r="J51" t="n">
+        <v>570</v>
+      </c>
+      <c r="P51" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>11</v>
+      </c>
+      <c r="X51" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>933</v>
+      </c>
+      <c r="G52" t="n">
+        <v>576</v>
+      </c>
+      <c r="H52" t="n">
+        <v>220</v>
+      </c>
+      <c r="I52" t="n">
+        <v>357</v>
+      </c>
+      <c r="J52" t="n">
+        <v>547</v>
+      </c>
+      <c r="P52" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2</v>
+      </c>
+      <c r="S52" t="n">
+        <v>11</v>
+      </c>
+      <c r="X52" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>625</v>
+      </c>
+      <c r="G53" t="n">
+        <v>386</v>
+      </c>
+      <c r="H53" t="n">
+        <v>147</v>
+      </c>
+      <c r="I53" t="n">
+        <v>239</v>
+      </c>
+      <c r="J53" t="n">
+        <v>367</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="X53" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>396</v>
+      </c>
+      <c r="G54" t="n">
+        <v>245</v>
+      </c>
+      <c r="H54" t="n">
+        <v>93</v>
+      </c>
+      <c r="I54" t="n">
+        <v>151</v>
+      </c>
+      <c r="J54" t="n">
+        <v>232</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="X54" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>339</v>
+      </c>
+      <c r="G55" t="n">
+        <v>209</v>
+      </c>
+      <c r="H55" t="n">
+        <v>80</v>
+      </c>
+      <c r="I55" t="n">
+        <v>130</v>
+      </c>
+      <c r="J55" t="n">
+        <v>199</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="X55" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>239</v>
+      </c>
+      <c r="G56" t="n">
+        <v>148</v>
+      </c>
+      <c r="H56" t="n">
+        <v>56</v>
+      </c>
+      <c r="I56" t="n">
+        <v>91</v>
+      </c>
+      <c r="J56" t="n">
+        <v>140</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>3</v>
+      </c>
+      <c r="X56" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>142</v>
+      </c>
+      <c r="G57" t="n">
+        <v>88</v>
+      </c>
+      <c r="H57" t="n">
+        <v>33</v>
+      </c>
+      <c r="I57" t="n">
+        <v>54</v>
+      </c>
+      <c r="J57" t="n">
+        <v>83</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="X57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" t="n">
+        <v>61</v>
+      </c>
+      <c r="H58" t="n">
+        <v>23</v>
+      </c>
+      <c r="I58" t="n">
+        <v>38</v>
+      </c>
+      <c r="J58" t="n">
+        <v>58</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>89</v>
+      </c>
+      <c r="G59" t="n">
+        <v>55</v>
+      </c>
+      <c r="H59" t="n">
+        <v>21</v>
+      </c>
+      <c r="I59" t="n">
+        <v>34</v>
+      </c>
+      <c r="J59" t="n">
+        <v>52</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>38514</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.0451</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1737</v>
+      </c>
+      <c r="L60" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="M60" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N60" t="n">
+        <v>920.6</v>
+      </c>
+      <c r="P60" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>7</v>
+      </c>
+      <c r="R60" t="n">
+        <v>13</v>
+      </c>
+      <c r="S60" t="n">
+        <v>76</v>
+      </c>
+      <c r="U60" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1206</v>
+      </c>
+      <c r="H61" t="n">
+        <v>471</v>
+      </c>
+      <c r="I61" t="n">
+        <v>735</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>1</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4</v>
+      </c>
+      <c r="S61" t="n">
+        <v>28</v>
+      </c>
+      <c r="X61" t="n">
+        <v>78</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1750</v>
+      </c>
+      <c r="G62" t="n">
+        <v>867</v>
+      </c>
+      <c r="H62" t="n">
+        <v>339</v>
+      </c>
+      <c r="I62" t="n">
+        <v>528</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3</v>
+      </c>
+      <c r="S62" t="n">
+        <v>20</v>
+      </c>
+      <c r="X62" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1343</v>
+      </c>
+      <c r="G63" t="n">
+        <v>666</v>
+      </c>
+      <c r="H63" t="n">
+        <v>260</v>
+      </c>
+      <c r="I63" t="n">
+        <v>406</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>15</v>
+      </c>
+      <c r="X63" t="n">
+        <v>43</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1068</v>
+      </c>
+      <c r="G64" t="n">
+        <v>530</v>
+      </c>
+      <c r="H64" t="n">
+        <v>207</v>
+      </c>
+      <c r="I64" t="n">
+        <v>323</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2</v>
+      </c>
+      <c r="S64" t="n">
+        <v>13</v>
+      </c>
+      <c r="X64" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>757</v>
+      </c>
+      <c r="G65" t="n">
+        <v>376</v>
+      </c>
+      <c r="H65" t="n">
+        <v>147</v>
+      </c>
+      <c r="I65" t="n">
+        <v>229</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>9</v>
+      </c>
+      <c r="X65" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>521</v>
+      </c>
+      <c r="G66" t="n">
+        <v>258</v>
+      </c>
+      <c r="H66" t="n">
+        <v>101</v>
+      </c>
+      <c r="I66" t="n">
+        <v>157</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6</v>
+      </c>
+      <c r="X66" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>355</v>
+      </c>
+      <c r="G67" t="n">
+        <v>176</v>
+      </c>
+      <c r="H67" t="n">
+        <v>69</v>
+      </c>
+      <c r="I67" t="n">
+        <v>107</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>4</v>
+      </c>
+      <c r="X67" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>301</v>
+      </c>
+      <c r="G68" t="n">
+        <v>149</v>
+      </c>
+      <c r="H68" t="n">
+        <v>58</v>
+      </c>
+      <c r="I68" t="n">
+        <v>91</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>4</v>
+      </c>
+      <c r="X68" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>200</v>
+      </c>
+      <c r="G69" t="n">
+        <v>99</v>
+      </c>
+      <c r="H69" t="n">
+        <v>39</v>
+      </c>
+      <c r="I69" t="n">
+        <v>60</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2</v>
+      </c>
+      <c r="X69" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2063</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1347</v>
+      </c>
+      <c r="H70" t="n">
+        <v>552</v>
+      </c>
+      <c r="I70" t="n">
+        <v>796</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>11</v>
+      </c>
+      <c r="X70" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1540</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1006</v>
+      </c>
+      <c r="H71" t="n">
+        <v>412</v>
+      </c>
+      <c r="I71" t="n">
+        <v>594</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>9</v>
+      </c>
+      <c r="X71" t="n">
+        <v>82</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1062</v>
+      </c>
+      <c r="G72" t="n">
+        <v>693</v>
+      </c>
+      <c r="H72" t="n">
+        <v>284</v>
+      </c>
+      <c r="I72" t="n">
+        <v>409</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="X72" t="n">
+        <v>57</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>743</v>
+      </c>
+      <c r="G73" t="n">
+        <v>485</v>
+      </c>
+      <c r="H73" t="n">
+        <v>199</v>
+      </c>
+      <c r="I73" t="n">
+        <v>286</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="X73" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>557</v>
+      </c>
+      <c r="G74" t="n">
+        <v>364</v>
+      </c>
+      <c r="H74" t="n">
+        <v>149</v>
+      </c>
+      <c r="I74" t="n">
+        <v>215</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="X74" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>336</v>
+      </c>
+      <c r="G75" t="n">
+        <v>220</v>
+      </c>
+      <c r="H75" t="n">
+        <v>90</v>
+      </c>
+      <c r="I75" t="n">
+        <v>130</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>273</v>
+      </c>
+      <c r="G76" t="n">
+        <v>179</v>
+      </c>
+      <c r="H76" t="n">
+        <v>73</v>
+      </c>
+      <c r="I76" t="n">
+        <v>105</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="X76" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>169</v>
+      </c>
+      <c r="G77" t="n">
+        <v>110</v>
+      </c>
+      <c r="H77" t="n">
+        <v>45</v>
+      </c>
+      <c r="I77" t="n">
+        <v>65</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1</v>
+      </c>
+      <c r="X77" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>130</v>
+      </c>
+      <c r="G78" t="n">
+        <v>85</v>
+      </c>
+      <c r="H78" t="n">
+        <v>35</v>
+      </c>
+      <c r="I78" t="n">
+        <v>50</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="X78" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2077</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1036</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1036</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1005</v>
+      </c>
+      <c r="P79" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>23</v>
+      </c>
+      <c r="X79" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>1546</v>
+      </c>
+      <c r="G80" t="n">
+        <v>772</v>
+      </c>
+      <c r="H80" t="n">
+        <v>772</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>748</v>
+      </c>
+      <c r="P80" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>17</v>
+      </c>
+      <c r="X80" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1121</v>
+      </c>
+      <c r="G81" t="n">
+        <v>559</v>
+      </c>
+      <c r="H81" t="n">
+        <v>559</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>543</v>
+      </c>
+      <c r="P81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>11</v>
+      </c>
+      <c r="X81" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>728</v>
+      </c>
+      <c r="G82" t="n">
+        <v>363</v>
+      </c>
+      <c r="H82" t="n">
+        <v>363</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>352</v>
+      </c>
+      <c r="P82" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>537</v>
+      </c>
+      <c r="G83" t="n">
+        <v>268</v>
+      </c>
+      <c r="H83" t="n">
+        <v>268</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>260</v>
+      </c>
+      <c r="P83" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="X83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>375</v>
+      </c>
+      <c r="G84" t="n">
+        <v>187</v>
+      </c>
+      <c r="H84" t="n">
+        <v>187</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>182</v>
+      </c>
+      <c r="P84" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3</v>
+      </c>
+      <c r="X84" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>316</v>
+      </c>
+      <c r="G85" t="n">
+        <v>158</v>
+      </c>
+      <c r="H85" t="n">
+        <v>158</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>153</v>
+      </c>
+      <c r="P85" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3</v>
+      </c>
+      <c r="X85" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>194</v>
+      </c>
+      <c r="G86" t="n">
+        <v>97</v>
+      </c>
+      <c r="H86" t="n">
+        <v>97</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>94</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>2</v>
+      </c>
+      <c r="X86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>17751</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1445</v>
+      </c>
+      <c r="L87" t="n">
+        <v>143</v>
+      </c>
+      <c r="M87" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3443.9</v>
+      </c>
+      <c r="P87" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>8</v>
+      </c>
+      <c r="R87" t="n">
+        <v>9</v>
+      </c>
+      <c r="S87" t="n">
+        <v>90</v>
+      </c>
+      <c r="U87" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2783</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1848</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1848</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1244</v>
+      </c>
+      <c r="P88" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>14</v>
+      </c>
+      <c r="S88" t="n">
+        <v>73</v>
+      </c>
+      <c r="X88" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1596</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1059</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>713</v>
+      </c>
+      <c r="P89" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="R89" t="n">
+        <v>8</v>
+      </c>
+      <c r="S89" t="n">
+        <v>42</v>
+      </c>
+      <c r="X89" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1133</v>
+      </c>
+      <c r="G90" t="n">
+        <v>752</v>
+      </c>
+      <c r="H90" t="n">
+        <v>752</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>506</v>
+      </c>
+      <c r="P90" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6</v>
+      </c>
+      <c r="S90" t="n">
+        <v>30</v>
+      </c>
+      <c r="X90" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>860</v>
+      </c>
+      <c r="G91" t="n">
+        <v>571</v>
+      </c>
+      <c r="H91" t="n">
+        <v>571</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>384</v>
+      </c>
+      <c r="P91" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" t="n">
+        <v>23</v>
+      </c>
+      <c r="X91" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>743</v>
+      </c>
+      <c r="G92" t="n">
+        <v>493</v>
+      </c>
+      <c r="H92" t="n">
+        <v>493</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>332</v>
+      </c>
+      <c r="P92" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>4</v>
+      </c>
+      <c r="S92" t="n">
+        <v>19</v>
+      </c>
+      <c r="X92" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>512</v>
+      </c>
+      <c r="G93" t="n">
+        <v>340</v>
+      </c>
+      <c r="H93" t="n">
+        <v>340</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>229</v>
+      </c>
+      <c r="P93" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>13</v>
+      </c>
+      <c r="X93" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>325</v>
+      </c>
+      <c r="G94" t="n">
+        <v>216</v>
+      </c>
+      <c r="H94" t="n">
+        <v>216</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>145</v>
+      </c>
+      <c r="P94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>9</v>
+      </c>
+      <c r="X94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228</v>
+      </c>
+      <c r="G95" t="n">
+        <v>151</v>
+      </c>
+      <c r="H95" t="n">
+        <v>151</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>102</v>
+      </c>
+      <c r="P95" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>6</v>
+      </c>
+      <c r="X95" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>148</v>
+      </c>
+      <c r="G96" t="n">
+        <v>98</v>
+      </c>
+      <c r="H96" t="n">
+        <v>98</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>66</v>
+      </c>
+      <c r="P96" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>4</v>
+      </c>
+      <c r="X96" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>123</v>
+      </c>
+      <c r="G97" t="n">
+        <v>82</v>
+      </c>
+      <c r="H97" t="n">
+        <v>82</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>55</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="S97" t="n">
+        <v>2</v>
+      </c>
+      <c r="X97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>20689</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1111</v>
+      </c>
+      <c r="L98" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="M98" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="N98" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>4</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6</v>
+      </c>
+      <c r="S98" t="n">
+        <v>34</v>
+      </c>
+      <c r="U98" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>795</v>
+      </c>
+      <c r="G99" t="n">
+        <v>514</v>
+      </c>
+      <c r="H99" t="n">
+        <v>514</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>350</v>
+      </c>
+      <c r="P99" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="n">
+        <v>8</v>
+      </c>
+      <c r="X99" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>634</v>
+      </c>
+      <c r="G100" t="n">
+        <v>410</v>
+      </c>
+      <c r="H100" t="n">
+        <v>410</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>279</v>
+      </c>
+      <c r="P100" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="n">
+        <v>7</v>
+      </c>
+      <c r="X100" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>408</v>
+      </c>
+      <c r="G101" t="n">
+        <v>264</v>
+      </c>
+      <c r="H101" t="n">
+        <v>264</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>180</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="X101" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>288</v>
+      </c>
+      <c r="G102" t="n">
+        <v>186</v>
+      </c>
+      <c r="H102" t="n">
+        <v>186</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>127</v>
+      </c>
+      <c r="P102" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2</v>
+      </c>
+      <c r="X102" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>220</v>
+      </c>
+      <c r="G103" t="n">
+        <v>143</v>
+      </c>
+      <c r="H103" t="n">
+        <v>143</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>97</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>2</v>
+      </c>
+      <c r="X103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>151</v>
+      </c>
+      <c r="G104" t="n">
+        <v>97</v>
+      </c>
+      <c r="H104" t="n">
+        <v>97</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>66</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="X104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>102</v>
+      </c>
+      <c r="G105" t="n">
+        <v>66</v>
+      </c>
+      <c r="H105" t="n">
+        <v>66</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>45</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1</v>
+      </c>
+      <c r="X105" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>73</v>
+      </c>
+      <c r="G106" t="n">
+        <v>47</v>
+      </c>
+      <c r="H106" t="n">
+        <v>47</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>32</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1</v>
+      </c>
+      <c r="X106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>54</v>
+      </c>
+      <c r="G107" t="n">
+        <v>35</v>
+      </c>
+      <c r="H107" t="n">
+        <v>35</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>24</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>41</v>
+      </c>
+      <c r="G108" t="n">
+        <v>27</v>
+      </c>
+      <c r="H108" t="n">
+        <v>27</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>18</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>12102</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="J109" t="n">
+        <v>616</v>
+      </c>
+      <c r="L109" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1633.4</v>
+      </c>
+      <c r="P109" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>3</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>35</v>
+      </c>
+      <c r="U109" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>792</v>
+      </c>
+      <c r="G110" t="n">
+        <v>363</v>
+      </c>
+      <c r="H110" t="n">
+        <v>363</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>1</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>11</v>
+      </c>
+      <c r="X110" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>686</v>
+      </c>
+      <c r="G111" t="n">
+        <v>314</v>
+      </c>
+      <c r="H111" t="n">
+        <v>314</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="n">
+        <v>9</v>
+      </c>
+      <c r="X111" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>378</v>
+      </c>
+      <c r="G112" t="n">
+        <v>174</v>
+      </c>
+      <c r="H112" t="n">
+        <v>174</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>6</v>
+      </c>
+      <c r="X112" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>353</v>
+      </c>
+      <c r="G113" t="n">
+        <v>162</v>
+      </c>
+      <c r="H113" t="n">
+        <v>162</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="n">
+        <v>4</v>
+      </c>
+      <c r="X113" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>201</v>
+      </c>
+      <c r="G114" t="n">
+        <v>92</v>
+      </c>
+      <c r="H114" t="n">
+        <v>92</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="n">
+        <v>2</v>
+      </c>
+      <c r="X114" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>182</v>
+      </c>
+      <c r="G115" t="n">
+        <v>83</v>
+      </c>
+      <c r="H115" t="n">
+        <v>83</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2</v>
+      </c>
+      <c r="X115" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>116</v>
+      </c>
+      <c r="G116" t="n">
+        <v>53</v>
+      </c>
+      <c r="H116" t="n">
+        <v>53</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>1</v>
+      </c>
+      <c r="X116" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>78</v>
+      </c>
+      <c r="G117" t="n">
+        <v>36</v>
+      </c>
+      <c r="H117" t="n">
+        <v>36</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>1</v>
+      </c>
+      <c r="X117" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1468</v>
+      </c>
+      <c r="G118" t="n">
+        <v>705</v>
+      </c>
+      <c r="H118" t="n">
+        <v>705</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>555</v>
+      </c>
+      <c r="P118" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>1</v>
+      </c>
+      <c r="R118" t="n">
+        <v>1</v>
+      </c>
+      <c r="S118" t="n">
+        <v>19</v>
+      </c>
+      <c r="X118" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>964</v>
+      </c>
+      <c r="G119" t="n">
+        <v>463</v>
+      </c>
+      <c r="H119" t="n">
+        <v>463</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>365</v>
+      </c>
+      <c r="P119" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>1</v>
+      </c>
+      <c r="S119" t="n">
+        <v>12</v>
+      </c>
+      <c r="X119" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>647</v>
+      </c>
+      <c r="G120" t="n">
+        <v>311</v>
+      </c>
+      <c r="H120" t="n">
+        <v>311</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>245</v>
+      </c>
+      <c r="P120" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>9</v>
+      </c>
+      <c r="X120" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>570</v>
+      </c>
+      <c r="G121" t="n">
+        <v>274</v>
+      </c>
+      <c r="H121" t="n">
+        <v>274</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>216</v>
+      </c>
+      <c r="P121" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>7</v>
+      </c>
+      <c r="X121" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>390</v>
+      </c>
+      <c r="G122" t="n">
+        <v>187</v>
+      </c>
+      <c r="H122" t="n">
+        <v>187</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>147</v>
+      </c>
+      <c r="P122" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>4</v>
+      </c>
+      <c r="X122" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>238</v>
+      </c>
+      <c r="G123" t="n">
+        <v>114</v>
+      </c>
+      <c r="H123" t="n">
+        <v>114</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>90</v>
+      </c>
+      <c r="P123" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3</v>
+      </c>
+      <c r="X123" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>219</v>
+      </c>
+      <c r="G124" t="n">
+        <v>105</v>
+      </c>
+      <c r="H124" t="n">
+        <v>105</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>83</v>
+      </c>
+      <c r="P124" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>3</v>
+      </c>
+      <c r="X124" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>125</v>
+      </c>
+      <c r="G125" t="n">
+        <v>60</v>
+      </c>
+      <c r="H125" t="n">
+        <v>60</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>47</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="X125" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>101</v>
+      </c>
+      <c r="G126" t="n">
+        <v>48</v>
+      </c>
+      <c r="H126" t="n">
+        <v>48</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>38</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>1</v>
+      </c>
+      <c r="X126" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>71</v>
+      </c>
+      <c r="G127" t="n">
+        <v>34</v>
+      </c>
+      <c r="H127" t="n">
+        <v>34</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>27</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
+      <c r="X127" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>58</v>
+      </c>
+      <c r="G128" t="n">
+        <v>28</v>
+      </c>
+      <c r="H128" t="n">
+        <v>28</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>22</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>1</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>9300</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="J129" t="n">
+        <v>705</v>
+      </c>
+      <c r="L129" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="M129" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1865.9</v>
+      </c>
+      <c r="P129" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>3</v>
+      </c>
+      <c r="S129" t="n">
+        <v>29</v>
+      </c>
+      <c r="U129" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>895</v>
+      </c>
+      <c r="G130" t="n">
+        <v>571</v>
+      </c>
+      <c r="H130" t="n">
+        <v>571</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>1</v>
+      </c>
+      <c r="R130" t="n">
+        <v>2</v>
+      </c>
+      <c r="S130" t="n">
+        <v>17</v>
+      </c>
+      <c r="X130" t="n">
+        <v>36</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>646</v>
+      </c>
+      <c r="G131" t="n">
+        <v>412</v>
+      </c>
+      <c r="H131" t="n">
+        <v>412</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>1</v>
+      </c>
+      <c r="S131" t="n">
+        <v>11</v>
+      </c>
+      <c r="X131" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>438</v>
+      </c>
+      <c r="G132" t="n">
+        <v>280</v>
+      </c>
+      <c r="H132" t="n">
+        <v>280</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" t="n">
+        <v>8</v>
+      </c>
+      <c r="X132" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>345</v>
+      </c>
+      <c r="G133" t="n">
+        <v>220</v>
+      </c>
+      <c r="H133" t="n">
+        <v>220</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>1</v>
+      </c>
+      <c r="S133" t="n">
+        <v>6</v>
+      </c>
+      <c r="X133" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>254</v>
+      </c>
+      <c r="G134" t="n">
+        <v>162</v>
+      </c>
+      <c r="H134" t="n">
+        <v>162</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>1</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="X134" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>161</v>
+      </c>
+      <c r="G135" t="n">
+        <v>103</v>
+      </c>
+      <c r="H135" t="n">
+        <v>103</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>2</v>
+      </c>
+      <c r="X135" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>114</v>
+      </c>
+      <c r="G136" t="n">
+        <v>73</v>
+      </c>
+      <c r="H136" t="n">
+        <v>73</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2</v>
+      </c>
+      <c r="X136" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>78</v>
+      </c>
+      <c r="G137" t="n">
+        <v>50</v>
+      </c>
+      <c r="H137" t="n">
+        <v>50</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1</v>
+      </c>
+      <c r="X137" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>59</v>
+      </c>
+      <c r="G138" t="n">
+        <v>38</v>
+      </c>
+      <c r="H138" t="n">
+        <v>38</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="X138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>3164</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1536</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1648</v>
+      </c>
+      <c r="P139" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6</v>
+      </c>
+      <c r="S139" t="n">
+        <v>35</v>
+      </c>
+      <c r="X139" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1962</v>
+      </c>
+      <c r="G140" t="n">
+        <v>953</v>
+      </c>
+      <c r="H140" t="n">
+        <v>953</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1022</v>
+      </c>
+      <c r="P140" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>1</v>
+      </c>
+      <c r="R140" t="n">
+        <v>4</v>
+      </c>
+      <c r="S140" t="n">
+        <v>22</v>
+      </c>
+      <c r="X140" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1648</v>
+      </c>
+      <c r="G141" t="n">
+        <v>801</v>
+      </c>
+      <c r="H141" t="n">
+        <v>801</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>859</v>
+      </c>
+      <c r="P141" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>1</v>
+      </c>
+      <c r="R141" t="n">
+        <v>3</v>
+      </c>
+      <c r="S141" t="n">
+        <v>18</v>
+      </c>
+      <c r="X141" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>962</v>
+      </c>
+      <c r="G142" t="n">
+        <v>467</v>
+      </c>
+      <c r="H142" t="n">
+        <v>467</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>502</v>
+      </c>
+      <c r="P142" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>1</v>
+      </c>
+      <c r="R142" t="n">
+        <v>2</v>
+      </c>
+      <c r="S142" t="n">
+        <v>11</v>
+      </c>
+      <c r="X142" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>825</v>
+      </c>
+      <c r="G143" t="n">
+        <v>401</v>
+      </c>
+      <c r="H143" t="n">
+        <v>401</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>430</v>
+      </c>
+      <c r="P143" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="X143" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>506</v>
+      </c>
+      <c r="G144" t="n">
+        <v>246</v>
+      </c>
+      <c r="H144" t="n">
+        <v>246</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>264</v>
+      </c>
+      <c r="P144" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>1</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="X144" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>463</v>
+      </c>
+      <c r="G145" t="n">
+        <v>225</v>
+      </c>
+      <c r="H145" t="n">
+        <v>225</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>241</v>
+      </c>
+      <c r="P145" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="X145" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>282</v>
+      </c>
+      <c r="G146" t="n">
+        <v>137</v>
+      </c>
+      <c r="H146" t="n">
+        <v>137</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>147</v>
+      </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>3</v>
+      </c>
+      <c r="X146" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>207</v>
+      </c>
+      <c r="G147" t="n">
+        <v>100</v>
+      </c>
+      <c r="H147" t="n">
+        <v>100</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>108</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3</v>
+      </c>
+      <c r="X147" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>172</v>
+      </c>
+      <c r="G148" t="n">
+        <v>84</v>
+      </c>
+      <c r="H148" t="n">
+        <v>84</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>90</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="X148" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>105</v>
+      </c>
+      <c r="G149" t="n">
+        <v>51</v>
+      </c>
+      <c r="H149" t="n">
+        <v>51</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>55</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>1</v>
+      </c>
+      <c r="X149" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>68</v>
+      </c>
+      <c r="G150" t="n">
+        <v>33</v>
+      </c>
+      <c r="H150" t="n">
+        <v>33</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>35</v>
+      </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>1</v>
+      </c>
+      <c r="X150" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>53</v>
+      </c>
+      <c r="G151" t="n">
+        <v>26</v>
+      </c>
+      <c r="H151" t="n">
+        <v>26</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>27</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>36</v>
+      </c>
+      <c r="G152" t="n">
+        <v>17</v>
+      </c>
+      <c r="H152" t="n">
+        <v>17</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>19</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>33733</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1491</v>
+      </c>
+      <c r="L153" t="n">
+        <v>22</v>
+      </c>
+      <c r="M153" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N153" t="n">
+        <v>546.7</v>
+      </c>
+      <c r="P153" t="n">
+        <v>66</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>4</v>
+      </c>
+      <c r="R153" t="n">
+        <v>4</v>
+      </c>
+      <c r="S153" t="n">
+        <v>74</v>
+      </c>
+      <c r="U153" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>653</v>
+      </c>
+      <c r="G154" t="n">
+        <v>486</v>
+      </c>
+      <c r="H154" t="n">
+        <v>486</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>1</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1</v>
+      </c>
+      <c r="S154" t="n">
+        <v>9</v>
+      </c>
+      <c r="X154" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>465</v>
+      </c>
+      <c r="G155" t="n">
+        <v>347</v>
+      </c>
+      <c r="H155" t="n">
+        <v>347</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5</v>
+      </c>
+      <c r="X155" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>323</v>
+      </c>
+      <c r="G156" t="n">
+        <v>241</v>
+      </c>
+      <c r="H156" t="n">
+        <v>241</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3</v>
+      </c>
+      <c r="X156" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>198</v>
+      </c>
+      <c r="G157" t="n">
+        <v>148</v>
+      </c>
+      <c r="H157" t="n">
+        <v>148</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>2</v>
+      </c>
+      <c r="X157" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>163</v>
+      </c>
+      <c r="G158" t="n">
+        <v>121</v>
+      </c>
+      <c r="H158" t="n">
+        <v>121</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="n">
+        <v>2</v>
+      </c>
+      <c r="X158" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>117</v>
+      </c>
+      <c r="G159" t="n">
+        <v>87</v>
+      </c>
+      <c r="H159" t="n">
+        <v>87</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="n">
+        <v>1</v>
+      </c>
+      <c r="X159" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>86</v>
+      </c>
+      <c r="G160" t="n">
+        <v>64</v>
+      </c>
+      <c r="H160" t="n">
+        <v>64</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
+        <v>1</v>
+      </c>
+      <c r="X160" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>49</v>
+      </c>
+      <c r="G161" t="n">
+        <v>36</v>
+      </c>
+      <c r="H161" t="n">
+        <v>36</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="n">
+        <v>1</v>
+      </c>
+      <c r="X161" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>45</v>
+      </c>
+      <c r="G162" t="n">
+        <v>33</v>
+      </c>
+      <c r="H162" t="n">
+        <v>33</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="X162" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>33</v>
+      </c>
+      <c r="G163" t="n">
+        <v>25</v>
+      </c>
+      <c r="H163" t="n">
+        <v>25</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="X163" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>23</v>
+      </c>
+      <c r="G164" t="n">
+        <v>18</v>
+      </c>
+      <c r="H164" t="n">
+        <v>18</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="n">
+        <v>0</v>
+      </c>
+      <c r="X164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>manual_export</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>15</v>
+      </c>
+      <c r="G165" t="n">
+        <v>11</v>
+      </c>
+      <c r="H165" t="n">
+        <v>11</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="X165" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AA2"/>
   <dataValidations count="2">
@@ -10743,7 +19759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10858,6 +19874,735 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P-Q1-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.025249</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.032376</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.013007</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P-Q1-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.010682</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.036897</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.015612</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>828</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1763</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2489</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2558</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.015659</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.006484</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P-Q1-03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1781</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P-Q1-04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.010901</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.024066</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.005451</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2232</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5384</v>
+      </c>
+      <c r="E7" t="n">
+        <v>7760</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8524</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.018603</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.021866</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.017935</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P-Q1-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1737</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1737</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1737</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P-Q1-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.023342</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.031966</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.017102</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>P-Q1-07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.007797</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.053397</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.06683</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2296</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3243</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3337</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.010589</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.010465</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P-Q1-08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1445</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1244</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2463</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3553</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3776</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.039394</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.021181</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.007308</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P-Q1-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1111</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1111</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1111</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>350</v>
+      </c>
+      <c r="D15" t="n">
+        <v>809</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1144</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1218</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.015092</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.014823</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.007826</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P-Q1-10</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>616</v>
+      </c>
+      <c r="D16" t="n">
+        <v>616</v>
+      </c>
+      <c r="E16" t="n">
+        <v>616</v>
+      </c>
+      <c r="F16" t="n">
+        <v>616</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P-Q1-11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.028191</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.031228</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.007048</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>555</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1165</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1701</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1835</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.026191</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.00907</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.009875</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P-Q1-12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>705</v>
+      </c>
+      <c r="D19" t="n">
+        <v>705</v>
+      </c>
+      <c r="E19" t="n">
+        <v>705</v>
+      </c>
+      <c r="F19" t="n">
+        <v>705</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P-Q1-13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.027763</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.039799</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.016763</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1648</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3529</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4966</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.022651</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.019612</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.019303</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P-Q1-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1491</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1491</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1491</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P-Q1-15</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.014842</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.054378</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.004947</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R2"/>
   <dataValidations count="4">

--- a/content/KPIM/02_campaigns/CMP-2026-Q1/CMP-2026-Q1.xlsx
+++ b/content/KPIM/02_campaigns/CMP-2026-Q1/CMP-2026-Q1.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -534,20 +534,24 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Tên cột</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Là TEXT THUẦN, không có icon — trùng khớp tuyệt đối với tên trong schema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>LUẬT VÀNG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Ô nền VÀNG ở hàng tiêu đề là cột của bạn — agent không bao giờ ghi đè.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH LÁ do script sinh — sửa tay sẽ bị ghi đè lần chạy sau.</t>
+          <t>Nền VÀNG ở hàng tiêu đề = CỦA BẠN — agent không bao giờ ghi đè.</t>
         </is>
       </c>
     </row>
@@ -555,23 +559,23 @@
       <c r="A7" s="1" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ô nền XANH DƯƠNG do agent sinh — bạn sửa thoải mái.</t>
+          <t>Nền XANH LÁ = script sinh, sửa tay sẽ bị ghi đè.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Nền XANH DƯƠNG = agent sinh, bạn sửa thoải mái.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Ô rỗng nghĩa là gì</t>
-        </is>
-      </c>
+      <c r="A9" s="1" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+          <t>Không nhớ màu? Mở sheet _Dictionary, cột 'ai ghi'.</t>
         </is>
       </c>
     </row>
@@ -582,140 +586,156 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>Ô rỗng nghĩa là gì</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ô rỗng nghĩa là CHƯA BIẾT. Không điền 0, không điền "N/A", không đoán. Riêng baseline_median rỗng = chưa đủ mẫu, dashboard phải hiện "chưa đủ mẫu".</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>01_Brief</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 trường của brief — Thay cho brief.yml. Brief là thứ BẠN duyệt nên phải nằm trong workbook, không nằm ở file cấu hình máy đọc.
 </t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>02_KPI_Target</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = campaign × kênh × pillar × chỉ số × kỳ — baseline_n &lt; 10 thì mọi so-sánh-với-median phải bị chặn. Đây là chỗ duy nhất giữ con số baseline — không được nhân bản sang sheet khác.
 </t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>03_Calendar</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset — Sheet trung tâm. Nhìn hết một chiến dịch trên một màn hình.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>04_Content</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 mảnh nội dung × 1 biến thể — Tách khỏi Calendar vì một asset có nhiều mảnh nội dung (title A/B, 3 caption, prompt media) và vì text dài làm dòng Calendar cao vài trăm pixel.
 </t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>05_Approval</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 asset × 1 vòng duyệt — Tách khỏi Calendar vì một asset duyệt nhiều vòng. Gộp một dòng là mất lịch sử revise — thứ đắt nhất khi rà lại sau chiến dịch.
 </t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>06_Publish_Log</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>1 dòng = 1 asset × 1 kênh × 1 lần chạy — Vết của mọi lần publish, kể cả dry-run và lần lỗi.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>07_Metrics_Daily</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = asset × kênh × ngày — Bản nạp lại của RIÊNG chiến dịch này (≈1.700 dòng cho 31 asset × 2 kênh × 28 ngày) để soi được ngay trong file. Nguồn sự thật vẫn là CSV ở data/&lt;instance&gt;/raw|star.
 </t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>08_Metrics_Summary</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>09_Leads</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>08_Metrics_Summary</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = asset × kênh — Chỗ trả lời câu "bài nào thắng, vì sao".</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>09_Leads</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1 dòng = 1 lead — Bỏ sheet này nếu chiến dịch không có mục tiêu lead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>10_Insights</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1 dòng = 1 phát hiện — Ép insight phải có bằng chứng. Không có evidence_metric + evidence_value thì không được ghi dòng — đây là chỗ AI hay bịa nhất.
 </t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Làm mới workbook</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>python scripts/workbook/build_workbook.py --campaign-id &lt;ID&gt; --out &lt;file&gt;</t>
         </is>
@@ -756,82 +776,82 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_id</t>
+          <t>lead_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source_raw</t>
+          <t>source_raw</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ created_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ need_type</t>
+          <t>need_type</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ product_interest</t>
+          <t>product_interest</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ region</t>
+          <t>region</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ branch</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_status</t>
+          <t>lead_status</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ priority_score</t>
+          <t>priority_score</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ lead_segment</t>
+          <t>lead_segment</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ next_action</t>
+          <t>next_action</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_duplicate_of</t>
+          <t>is_duplicate_of</t>
         </is>
       </c>
     </row>
@@ -877,72 +897,72 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 insight_id</t>
+          <t>insight_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope</t>
+          <t>scope</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 scope_ref</t>
+          <t>scope_ref</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 observed_at</t>
+          <t>observed_at</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 symptom</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_metric</t>
+          <t>evidence_metric</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 evidence_value</t>
+          <t>evidence_value</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_value</t>
+          <t>baseline_value</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 likely_cause</t>
+          <t>likely_cause</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 impact</t>
+          <t>impact</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recommendation</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 priority</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 status</t>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6400,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6417,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6439,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6456,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6449,7 +6469,7 @@
       <c r="B6" s="5" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6486,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6503,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6516,7 @@
       <c r="B9" s="5" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6531,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6546,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6563,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6555,12 +6575,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Số đăng ký mở thẻ</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6572,12 +6592,12 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Chi phí trên mỗi lead (CPL)</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6610,7 @@
       <c r="B15" s="5" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6623,7 @@
       <c r="B16" s="5" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6636,7 @@
       <c r="B17" s="4" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6629,7 +6649,7 @@
       <c r="B18" s="4" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6649,7 +6669,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6682,7 @@
       <c r="B20" s="5" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6675,7 +6695,7 @@
       <c r="B21" s="5" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6708,7 @@
       <c r="B22" s="4" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6701,7 +6721,7 @@
       <c r="B23" s="4" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>⚙️ script</t>
+          <t>script</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6738,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>🤖 agent</t>
+          <t>agent</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6755,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>👤 human</t>
+          <t>human</t>
         </is>
       </c>
     </row>
@@ -6768,52 +6788,52 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_code</t>
+          <t>pillar_code</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 metric_name</t>
+          <t>metric_name</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 period</t>
+          <t>period</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 target_value</t>
+          <t>target_value</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 unit</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_median</t>
+          <t>baseline_median</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_source</t>
+          <t>baseline_source</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ baseline_n</t>
+          <t>baseline_n</t>
         </is>
       </c>
     </row>
@@ -8182,212 +8202,212 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 campaign_id</t>
+          <t>campaign_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 series_id</t>
+          <t>series_id</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 episode_no</t>
+          <t>episode_no</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 week_no</t>
+          <t>week_no</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>🤖 parent_asset_id</t>
+          <t>parent_asset_id</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 doc_ref</t>
+          <t>doc_ref</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_primary</t>
+          <t>pillar_primary</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 pillar_secondary</t>
+          <t>pillar_secondary</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 persona_target</t>
+          <t>persona_target</t>
         </is>
       </c>
       <c r="K1" s="8" t="inlineStr">
         <is>
-          <t>🤖 format</t>
+          <t>format</t>
         </is>
       </c>
       <c r="L1" s="8" t="inlineStr">
         <is>
-          <t>🤖 platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="M1" s="8" t="inlineStr">
         <is>
-          <t>🤖 distribution_platforms</t>
+          <t>distribution_platforms</t>
         </is>
       </c>
       <c r="N1" s="8" t="inlineStr">
         <is>
-          <t>🤖 funnel_stage</t>
+          <t>funnel_stage</t>
         </is>
       </c>
       <c r="O1" s="8" t="inlineStr">
         <is>
-          <t>🤖 function_role</t>
+          <t>function_role</t>
         </is>
       </c>
       <c r="P1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_draft</t>
+          <t>title_draft</t>
         </is>
       </c>
       <c r="Q1" s="8" t="inlineStr">
         <is>
-          <t>🤖 title_final</t>
+          <t>title_final</t>
         </is>
       </c>
       <c r="R1" s="8" t="inlineStr">
         <is>
-          <t>🤖 cta_type</t>
+          <t>cta_type</t>
         </is>
       </c>
       <c r="S1" s="8" t="inlineStr">
         <is>
-          <t>🤖 has_commercial_cta</t>
+          <t>has_commercial_cta</t>
         </is>
       </c>
       <c r="T1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ hashtag_count</t>
+          <t>hashtag_count</t>
         </is>
       </c>
       <c r="V1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_date</t>
+          <t>planned_publish_date</t>
         </is>
       </c>
       <c r="W1" s="8" t="inlineStr">
         <is>
-          <t>🤖 planned_publish_time</t>
+          <t>planned_publish_time</t>
         </is>
       </c>
       <c r="X1" s="8" t="inlineStr">
         <is>
-          <t>🤖 timezone</t>
+          <t>timezone</t>
         </is>
       </c>
       <c r="Y1" s="9" t="inlineStr">
         <is>
-          <t>👤 tos_score</t>
+          <t>tos_score</t>
         </is>
       </c>
       <c r="Z1" s="9" t="inlineStr">
         <is>
-          <t>👤 hrs_score</t>
+          <t>hrs_score</t>
         </is>
       </c>
       <c r="AA1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_topic</t>
+          <t>approve_topic</t>
         </is>
       </c>
       <c r="AB1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_content</t>
+          <t>approve_content</t>
         </is>
       </c>
       <c r="AC1" s="9" t="inlineStr">
         <is>
-          <t>👤 approve_final</t>
+          <t>approve_final</t>
         </is>
       </c>
       <c r="AD1" s="8" t="inlineStr">
         <is>
-          <t>🤖 status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="AE1" s="8" t="inlineStr">
         <is>
-          <t>🤖 owner</t>
+          <t>owner</t>
         </is>
       </c>
       <c r="AF1" s="8" t="inlineStr">
         <is>
-          <t>🤖 verification_open</t>
+          <t>verification_open</t>
         </is>
       </c>
       <c r="AG1" s="9" t="inlineStr">
         <is>
-          <t>👤 qa_passed</t>
+          <t>qa_passed</t>
         </is>
       </c>
       <c r="AH1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_by</t>
+          <t>approved_by</t>
         </is>
       </c>
       <c r="AI1" s="9" t="inlineStr">
         <is>
-          <t>👤 approved_at</t>
+          <t>approved_at</t>
         </is>
       </c>
       <c r="AJ1" s="8" t="inlineStr">
         <is>
-          <t>🤖 blocked_reason</t>
+          <t>blocked_reason</t>
         </is>
       </c>
       <c r="AK1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ actual_publish_datetime</t>
+          <t>actual_publish_datetime</t>
         </is>
       </c>
       <c r="AL1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="AM1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="AN1" s="8" t="inlineStr">
         <is>
-          <t>🤖 playlist_id</t>
+          <t>playlist_id</t>
         </is>
       </c>
       <c r="AO1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_source_id</t>
+          <t>recycle_source_id</t>
         </is>
       </c>
       <c r="AP1" s="8" t="inlineStr">
         <is>
-          <t>🤖 recycle_due_date</t>
+          <t>recycle_due_date</t>
         </is>
       </c>
     </row>
@@ -9411,34 +9431,14 @@
           <t>x</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>need_review</t>
+          <t>drafted</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>Team Marketing KPIM Bank</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>UAT demo</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:31</t>
         </is>
       </c>
     </row>
@@ -9888,7 +9888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9908,242 +9908,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_id</t>
+          <t>content_id</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>🤖 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>🤖 content_type</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 variant</t>
+          <t>variant</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>🤖 body</t>
+          <t>body</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ char_count</t>
+          <t>char_count</t>
         </is>
       </c>
       <c r="G1" s="8" t="inlineStr">
         <is>
-          <t>🤖 hashtags</t>
+          <t>hashtags</t>
         </is>
       </c>
       <c r="H1" s="8" t="inlineStr">
         <is>
-          <t>🤖 language</t>
+          <t>language</t>
         </is>
       </c>
       <c r="I1" s="8" t="inlineStr">
         <is>
-          <t>🤖 draft_path</t>
+          <t>draft_path</t>
         </is>
       </c>
       <c r="J1" s="8" t="inlineStr">
         <is>
-          <t>🤖 ai_generated</t>
+          <t>ai_generated</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ generated_at</t>
+          <t>generated_at</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 is_selected</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P-Q1-18-script-final</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P-Q1-18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>script</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># P-Q1-18 · Reel · Tuần lễ hoàn tiền siêu thị
-**Chức năng riêng:** mở vấn đề — người xem tự thấy mình đang bỏ sót tiền, chưa bán gì.
-**Pillar:** Promo · **Funnel:** discovery · **Thời lượng đích:** 24–28 giây
----
-## Hook (0–2s)
-&gt; Mỗi tháng bạn tiêu 6 triệu đi siêu thị. Bạn đang bỏ lại bao nhiêu trên bàn?
-## Kịch bản
-| Mốc | Hình | Lời |
-|---|---|---|
-| 0–2s | Cận cảnh hoá đơn siêu thị dài | Mỗi tháng bạn tiêu 6 triệu đi siêu thị. Bạn đang bỏ lại bao nhiêu trên bàn? |
-| 2–8s | Tay quẹt thẻ, số tiền hiện lên | Hoàn tiền 5% nghe thì nhỏ. Nhưng 5% của 6 triệu là 300 nghìn. Một tháng. |
-| 8–16s | Chồng 12 hoá đơn xếp lên | Nhân 12 tháng. Bằng đúng một lần đi chợ Tết. Tiền đó vốn đã là của bạn — chỉ là bạn chưa nhận. |
-| 16–24s | Màn hình app hiện mức hoàn | Tuần lễ này mức hoàn tối đa là 500 nghìn. Hết hạn mức thì thôi, không cộng dồn sang tháng sau. `[KIỂM CHỨNG 1]` |
-| 24–28s | Logo + dòng điều kiện | Xem điều kiện áp dụng trước khi đăng ký. Đọc kỹ phần hạn mức. |
-## Ghi chú sản xuất
-- Không quay mặt người thật, không hiện số thẻ, không hiện tên chủ thẻ.
-- Con số 6 triệu là **ví dụ minh hoạ**, phải hiện chữ "ví dụ" trên màn hình — không được
-  để người xem hiểu là mức chi tiêu trung bình có thật.
-- Chữ tiếng Việt overlay lúc dựng, không để model sinh chữ trong ảnh.
-## `[KIỂM CHỨNG]` còn mở
-1. **Hạn mức 500.000đ có cộng dồn sang kỳ sau không?** Phải lấy xác nhận từ biểu phí
-   chính thức trước khi quay. Nếu có cộng dồn thì câu ở mốc 16–24s sai và phải viết lại.
-## Mục QA chưa tự tin đạt
-- `chk_primary_source`: mức hoàn 5% và trần 500.000đ đang lấy từ tiêu đề kế hoạch, **chưa
-  đối chiếu biểu phí**. Cần link biểu phí trước khi qua cổng duyệt nội dung.
-- `chk_cta_ok`: chưa rõ chiến dịch này có được phép CTA thương mại trực tiếp không —
-  `01_Brief.commercial_cta_episodes` của CMP-2026-Q1 cần người xác nhận.
-</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1845</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>drafts/P-Q1-18-script.md</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P-Q1-18-caption-final</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P-Q1-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>caption</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5% của 6 triệu tiền chợ là 300 nghìn một tháng — con số nhỏ đến mức hầu hết mọi người không buồn tính, rồi nhân 12 tháng thì đúng bằng một lần đi chợ Tết.
-Tuần này trần hoàn tiền siêu thị là 500.000đ, không cộng dồn sang kỳ sau. Hết hạn mức là thôi.
-Đọc kỹ phần hạn mức trong biểu phí trước khi đăng ký — chỗ đó quyết định bạn thật sự nhận lại bao nhiêu.
-</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>357</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>#KPIMBank #HoanTien #TheTinDung #ChiTieuThongMinh</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:15</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P-Q1-18-hook-final</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>P-Q1-18</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>hook</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Moi thang ban tieu 6 trieu di sieu thi. Ban dang bo lai bao nhieu tren ban?</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>75</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>vi</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:16</t>
+          <t>is_selected</t>
         </is>
       </c>
     </row>
@@ -10173,7 +9993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10199,92 +10019,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>👤 review_id</t>
+          <t>review_id</t>
         </is>
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>👤 asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>👤 round_no</t>
+          <t>round_no</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>🤖 submitted_at</t>
+          <t>submitted_at</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>👤 reviewer</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision</t>
+          <t>decision</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>👤 decided_at</t>
+          <t>decided_at</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>👤 comment</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_primary_source</t>
+          <t>chk_primary_source</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_fact_opinion</t>
+          <t>chk_fact_opinion</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_title_no_overclaim</t>
+          <t>chk_title_no_overclaim</t>
         </is>
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_thumbnail_honest</t>
+          <t>chk_thumbnail_honest</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_subscribe_reason</t>
+          <t>chk_subscribe_reason</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_next_bridge</t>
+          <t>chk_next_bridge</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_hashtag_ok</t>
+          <t>chk_hashtag_ok</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_cta_ok</t>
+          <t>chk_cta_ok</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_internal_tool</t>
+          <t>chk_no_internal_tool</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 chk_no_pii</t>
+          <t>chk_no_pii</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10124,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UAT demo</t>
+          <t>UAT icon-free</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -10314,49 +10134,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-21 22:57:17</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Duyet chu de de chay thu</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P-Q1-18-R2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>P-Q1-18</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>UAT demo</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:31</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Duyet cuoi de chay thu</t>
-        </is>
-      </c>
+          <t>2026-07-21 23:53:58</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:R2"/>
@@ -10405,7 +10186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10425,102 +10206,62 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ run_id</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ attempt_no</t>
+          <t>attempt_no</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ mode</t>
+          <t>mode</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ autonomy_at_run</t>
+          <t>autonomy_at_run</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ requested_at</t>
+          <t>requested_at</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ scheduled_for</t>
+          <t>scheduled_for</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform_native_id</t>
+          <t>platform_native_id</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ live_url</t>
+          <t>live_url</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ error_message</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P-Q1-18-facebook-1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>P-Q1-18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>dry_run</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>suggest</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-07-21 22:58:32</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>skipped</t>
+          <t>error_message</t>
         </is>
       </c>
     </row>
@@ -10585,137 +10326,137 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ date</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ source</t>
+          <t>source</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ impressions</t>
+          <t>impressions</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach</t>
+          <t>reach</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_organic</t>
+          <t>reach_organic</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ reach_paid</t>
+          <t>reach_paid</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ views</t>
+          <t>views</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engaged_views</t>
+          <t>engaged_views</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_view_duration_sec</t>
+          <t>avg_view_duration_sec</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ avg_percentage_viewed</t>
+          <t>avg_percentage_viewed</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ watch_time_min</t>
+          <t>watch_time_min</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ likes</t>
+          <t>likes</t>
         </is>
       </c>
       <c r="Q1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="R1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ shares</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="S1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_total</t>
+          <t>engagement_total</t>
         </is>
       </c>
       <c r="T1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ poll_votes</t>
+          <t>poll_votes</t>
         </is>
       </c>
       <c r="U1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subscribers_gained</t>
+          <t>subscribers_gained</t>
         </is>
       </c>
       <c r="V1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ related_video_clicks</t>
+          <t>related_video_clicks</t>
         </is>
       </c>
       <c r="W1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ returning_viewers</t>
+          <t>returning_viewers</t>
         </is>
       </c>
       <c r="X1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ clicks_total</t>
+          <t>clicks_total</t>
         </is>
       </c>
       <c r="Y1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_clicks</t>
+          <t>cta_clicks</t>
         </is>
       </c>
       <c r="Z1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ leads</t>
+          <t>leads</t>
         </is>
       </c>
       <c r="AA1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cost</t>
+          <t>cost</t>
         </is>
       </c>
     </row>
@@ -19785,92 +19526,92 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ asset_id</t>
+          <t>asset_id</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ platform</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m24h_views</t>
+          <t>m24h_views</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m72h_views</t>
+          <t>m72h_views</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m7d_views</t>
+          <t>m7d_views</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ m28d_views</t>
+          <t>m28d_views</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ engagement_rate</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ ctr</t>
+          <t>ctr</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ cta_rate</t>
+          <t>cta_rate</t>
         </is>
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ subs_per_1000_engaged</t>
+          <t>subs_per_1000_engaged</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ retention_30s</t>
+          <t>retention_30s</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_primary</t>
+          <t>vs_median_primary</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ vs_median_secondary</t>
+          <t>vs_median_secondary</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ kpi_hit_count</t>
+          <t>kpi_hit_count</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ guardrail_ok</t>
+          <t>guardrail_ok</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>⚙️ is_winner</t>
+          <t>is_winner</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_28d</t>
+          <t>decision_28d</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>👤 decision_note</t>
+          <t>decision_note</t>
         </is>
       </c>
     </row>
